--- a/tools/importer/reports/import-footer.report.xlsx
+++ b/tools/importer/reports/import-footer.report.xlsx
@@ -55,7 +55,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-09-29T10:44:59.771Z</t>
+    <t>2026-09-29T11:58:36.364Z</t>
   </si>
   <si>
     <t>https://www1.vhi.ie/about/media-releases-and-publications/2015/11</t>
@@ -67,7 +67,7 @@
     <t>nav</t>
   </si>
   <si>
-    <t>2026-09-29T10:13:10.419Z</t>
+    <t>2026-09-29T11:58:25.956Z</t>
   </si>
   <si>
     <t>about/media-releases-and-publications/2015/11.report.json</t>
